--- a/forms/app/quality_monitoring_planning.xlsx
+++ b/forms/app/quality_monitoring_planning.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20387"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20389"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D-tree\config-dtree-newrepo\config-dtree\forms\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC73CDB3-B6D6-4300-A04E-388F3418048E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE45B79-B99D-4AB7-B257-552F5E42FBFC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="91">
   <si>
     <t>type</t>
   </si>
@@ -168,9 +168,6 @@
     <t>. &gt; today()</t>
   </si>
   <si>
-    <t>Date cannot be a past date or today</t>
-  </si>
-  <si>
     <t>group_summary</t>
   </si>
   <si>
@@ -291,6 +288,15 @@
   </si>
   <si>
     <t>Kazi ya ufuatiliaji wa ubora kwaajili ya ${chw_name} itatokea tarehe *_${c_formatted_task_date}_*.</t>
+  </si>
+  <si>
+    <t>Maelezo ya ufuatiliaji</t>
+  </si>
+  <si>
+    <t>Please choose a future date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tafadhali chagua tarehe ya mbele </t>
   </si>
 </sst>
 </file>
@@ -1241,7 +1247,9 @@
       <c r="C19" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="5"/>
+      <c r="D19" s="5" t="s">
+        <v>88</v>
+      </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
       <c r="G19" s="4" t="s">
@@ -1278,7 +1286,7 @@
         <v>45</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>46</v>
@@ -1288,9 +1296,11 @@
         <v>47</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
-      <c r="J20" s="5"/>
+      <c r="J20" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="K20" s="5"/>
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
@@ -1373,18 +1383,18 @@
         <v>13</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>50</v>
-      </c>
       <c r="D23" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
       <c r="G23" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
@@ -1408,21 +1418,21 @@
     </row>
     <row r="24" spans="1:26" ht="39" x14ac:dyDescent="0.6">
       <c r="A24" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="C24" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>54</v>
-      </c>
       <c r="D24" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
       <c r="G24" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
@@ -1446,16 +1456,16 @@
     </row>
     <row r="25" spans="1:26" ht="104" x14ac:dyDescent="0.6">
       <c r="A25" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B25" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="D25" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
@@ -1482,21 +1492,21 @@
     </row>
     <row r="26" spans="1:26" ht="26" x14ac:dyDescent="0.6">
       <c r="A26" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B26" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>59</v>
-      </c>
       <c r="D26" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
       <c r="G26" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
@@ -1523,13 +1533,13 @@
         <v>22</v>
       </c>
       <c r="B27" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="4" t="s">
-        <v>62</v>
-      </c>
       <c r="D27" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
@@ -1538,7 +1548,7 @@
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
       <c r="K27" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L27" s="5"/>
       <c r="M27" s="5"/>
@@ -1558,16 +1568,16 @@
     </row>
     <row r="28" spans="1:26" ht="52" x14ac:dyDescent="0.6">
       <c r="A28" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B28" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C28" s="4" t="s">
-        <v>65</v>
-      </c>
       <c r="D28" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
@@ -1597,13 +1607,13 @@
         <v>22</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
@@ -1612,7 +1622,7 @@
       <c r="I29" s="5"/>
       <c r="J29" s="5"/>
       <c r="K29" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L29" s="5"/>
       <c r="M29" s="5"/>
@@ -1632,16 +1642,16 @@
     </row>
     <row r="30" spans="1:26" ht="78" x14ac:dyDescent="0.6">
       <c r="A30" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B30" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C30" s="4" t="s">
-        <v>69</v>
-      </c>
       <c r="D30" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
@@ -1671,7 +1681,7 @@
         <v>35</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
@@ -28832,6 +28842,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -28845,7 +28856,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>1</v>
@@ -28897,22 +28908,22 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
@@ -28937,23 +28948,23 @@
     </row>
     <row r="2" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A2" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C2" s="9">
         <f ca="1">NOW()</f>
-        <v>44778.414911574073</v>
+        <v>44825.561099421298</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>80</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>81</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
